--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mcartwright/git/sinc-laboratory.github.io/markdown_generator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sripathisridhar/Documents/code/sinc-laboratory.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAEE6D0-6406-8B44-96BA-A0CF51757F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC652C4E-87EE-F54A-A6CB-481A1EA3DB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="2480" windowWidth="27740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2100" yWindow="2140" windowWidth="27740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="348">
   <si>
     <t>title</t>
   </si>
@@ -1049,6 +1049,21 @@
   </si>
   <si>
     <t>right</t>
+  </si>
+  <si>
+    <t>Multi-label Open-set Audio Classification</t>
+  </si>
+  <si>
+    <t>sridhar2023multi.pdf</t>
+  </si>
+  <si>
+    <t>Current audio classification models have small class vocabularies relative to the large number of sound event classes of interest in the real world. Thus, they provide a limited view of the world that may miss important yet unexpected or unknown sound events. To address this issue, open-set audio classification techniques have been developed to detect sound events from unknown classes. Although these methods have been applied to a multi-class context in audio, such as sound scene classification, they have yet to be investigated for polyphonic audio in which sound events overlap, requiring the use of multi-label models. In this study, we establish the problem of multi-label open-set audio classification by creating a dataset with varying unknown class distributions and evaluating baseline approaches built upon existing techniques.</t>
+  </si>
+  <si>
+    <t>sridhar_dcase23_model.png</t>
+  </si>
+  <si>
+    <t>Sridhar, S., and Cartwright, M. Multi-label Open-set Audio Classification. In &lt;i&gt;Proceedings of the Workshop on Detection and Classification of Acoustic Scenes and Events (DCASE)&lt;/i&gt;, 2023.</t>
   </si>
 </sst>
 </file>
@@ -1551,13 +1566,11 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1618,9 +1631,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1658,7 +1671,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1764,7 +1777,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1906,7 +1919,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1914,18 +1927,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="10.83203125" style="2"/>
     <col min="2" max="2" width="17.83203125" customWidth="1"/>
     <col min="3" max="4" width="76.6640625" customWidth="1"/>
     <col min="6" max="6" width="51.1640625" customWidth="1"/>
-    <col min="7" max="7" width="73.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="73.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>167</v>
       </c>
       <c r="B1" t="s">
@@ -1943,7 +1956,7 @@
       <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
       <c r="H1" t="s">
@@ -1981,7 +1994,7 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>43678</v>
       </c>
       <c r="B2" t="s">
@@ -1999,7 +2012,7 @@
       <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>9</v>
       </c>
       <c r="R2" t="s">
@@ -2007,7 +2020,7 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>43739</v>
       </c>
       <c r="B3" t="s">
@@ -2025,7 +2038,7 @@
       <c r="F3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>13</v>
       </c>
       <c r="H3" t="s">
@@ -2048,7 +2061,7 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>43739</v>
       </c>
       <c r="B4" t="s">
@@ -2066,7 +2079,7 @@
       <c r="F4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>20</v>
       </c>
       <c r="H4" t="s">
@@ -2086,7 +2099,7 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>43739</v>
       </c>
       <c r="B5" t="s">
@@ -2104,7 +2117,7 @@
       <c r="F5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" t="s">
         <v>200</v>
       </c>
       <c r="H5" t="s">
@@ -2121,7 +2134,7 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>43466</v>
       </c>
       <c r="B6" t="s">
@@ -2139,13 +2152,13 @@
       <c r="F6" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" t="s">
         <v>30</v>
       </c>
       <c r="H6" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6">
         <v>66</v>
       </c>
       <c r="N6" t="s">
@@ -2159,7 +2172,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>43586</v>
       </c>
       <c r="B7" t="s">
@@ -2177,7 +2190,7 @@
       <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" t="s">
         <v>35</v>
       </c>
       <c r="R7" t="s">
@@ -2185,7 +2198,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>43556</v>
       </c>
       <c r="B8" t="s">
@@ -2203,7 +2216,7 @@
       <c r="F8" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" t="s">
         <v>39</v>
       </c>
       <c r="H8" t="s">
@@ -2220,7 +2233,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>43556</v>
       </c>
       <c r="B9" t="s">
@@ -2238,7 +2251,7 @@
       <c r="F9" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" t="s">
         <v>43</v>
       </c>
       <c r="H9" t="s">
@@ -2255,7 +2268,7 @@
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>43466</v>
       </c>
       <c r="B10" t="s">
@@ -2273,7 +2286,7 @@
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" t="s">
         <v>50</v>
       </c>
       <c r="R10" t="s">
@@ -2281,7 +2294,7 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>43466</v>
       </c>
       <c r="B11" t="s">
@@ -2299,7 +2312,7 @@
       <c r="F11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" t="s">
         <v>55</v>
       </c>
       <c r="R11" t="s">
@@ -2307,7 +2320,7 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>43344</v>
       </c>
       <c r="B12" t="s">
@@ -2325,7 +2338,7 @@
       <c r="F12" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" t="s">
         <v>59</v>
       </c>
       <c r="H12" t="s">
@@ -2348,7 +2361,7 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>43191</v>
       </c>
       <c r="B13" t="s">
@@ -2366,7 +2379,7 @@
       <c r="F13" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" t="s">
         <v>130</v>
       </c>
       <c r="H13" t="s">
@@ -2392,7 +2405,7 @@
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>43191</v>
       </c>
       <c r="B14" t="s">
@@ -2410,7 +2423,7 @@
       <c r="F14" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" t="s">
         <v>133</v>
       </c>
       <c r="L14" t="s">
@@ -2424,7 +2437,7 @@
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>43040</v>
       </c>
       <c r="B15" t="s">
@@ -2442,7 +2455,7 @@
       <c r="F15" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" t="s">
         <v>139</v>
       </c>
       <c r="H15" t="s">
@@ -2471,7 +2484,7 @@
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>43009</v>
       </c>
       <c r="B16" t="s">
@@ -2489,13 +2502,13 @@
       <c r="F16" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" t="s">
         <v>141</v>
       </c>
       <c r="H16" t="s">
         <v>142</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16">
         <v>50</v>
       </c>
       <c r="N16" s="1" t="s">
@@ -2515,7 +2528,7 @@
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>42705</v>
       </c>
       <c r="B17" t="s">
@@ -2533,7 +2546,7 @@
       <c r="F17" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" t="s">
         <v>173</v>
       </c>
       <c r="R17" t="s">
@@ -2541,7 +2554,7 @@
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>42583</v>
       </c>
       <c r="B18" t="s">
@@ -2559,7 +2572,7 @@
       <c r="F18" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" t="s">
         <v>145</v>
       </c>
       <c r="R18" t="s">
@@ -2567,7 +2580,7 @@
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>42491</v>
       </c>
       <c r="B19" t="s">
@@ -2585,7 +2598,7 @@
       <c r="F19" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" t="s">
         <v>146</v>
       </c>
       <c r="R19" t="s">
@@ -2593,7 +2606,7 @@
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>42461</v>
       </c>
       <c r="B20" t="s">
@@ -2611,7 +2624,7 @@
       <c r="F20" t="s">
         <v>88</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" t="s">
         <v>147</v>
       </c>
       <c r="H20" t="s">
@@ -2637,7 +2650,7 @@
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
+      <c r="A21" s="2">
         <v>42278</v>
       </c>
       <c r="B21" t="s">
@@ -2655,13 +2668,13 @@
       <c r="F21" t="s">
         <v>91</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" t="s">
         <v>188</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" t="s">
         <v>185</v>
       </c>
       <c r="J21">
@@ -2672,7 +2685,7 @@
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>42125</v>
       </c>
       <c r="B22" t="s">
@@ -2690,7 +2703,7 @@
       <c r="F22" t="s">
         <v>93</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" t="s">
         <v>150</v>
       </c>
       <c r="H22" t="s">
@@ -2713,7 +2726,7 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
+      <c r="A23" s="2">
         <v>42125</v>
       </c>
       <c r="B23" t="s">
@@ -2731,7 +2744,7 @@
       <c r="F23" t="s">
         <v>96</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" t="s">
         <v>153</v>
       </c>
       <c r="R23" t="s">
@@ -2739,7 +2752,7 @@
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
+      <c r="A24" s="2">
         <v>41944</v>
       </c>
       <c r="B24" t="s">
@@ -2757,7 +2770,7 @@
       <c r="F24" t="s">
         <v>98</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" t="s">
         <v>156</v>
       </c>
       <c r="K24" t="s">
@@ -2768,7 +2781,7 @@
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
+      <c r="A25" s="2">
         <v>41821</v>
       </c>
       <c r="B25" t="s">
@@ -2786,7 +2799,7 @@
       <c r="F25" t="s">
         <v>100</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" t="s">
         <v>157</v>
       </c>
       <c r="K25" t="s">
@@ -2797,7 +2810,7 @@
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
+      <c r="A26" s="2">
         <v>41760</v>
       </c>
       <c r="B26" t="s">
@@ -2815,7 +2828,7 @@
       <c r="F26" t="s">
         <v>104</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" t="s">
         <v>174</v>
       </c>
       <c r="R26" t="s">
@@ -2823,7 +2836,7 @@
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
+      <c r="A27" s="2">
         <v>41730</v>
       </c>
       <c r="B27" t="s">
@@ -2841,7 +2854,7 @@
       <c r="F27" t="s">
         <v>107</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" t="s">
         <v>158</v>
       </c>
       <c r="K27" t="s">
@@ -2852,7 +2865,7 @@
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
+      <c r="A28" s="2">
         <v>41579</v>
       </c>
       <c r="B28" t="s">
@@ -2870,7 +2883,7 @@
       <c r="F28" t="s">
         <v>110</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" t="s">
         <v>159</v>
       </c>
       <c r="H28" t="s">
@@ -2884,7 +2897,7 @@
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
+      <c r="A29" s="2">
         <v>41214</v>
       </c>
       <c r="B29" t="s">
@@ -2902,7 +2915,7 @@
       <c r="F29" t="s">
         <v>113</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" t="s">
         <v>160</v>
       </c>
       <c r="R29" t="s">
@@ -2910,7 +2923,7 @@
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
+      <c r="A30" s="2">
         <v>41091</v>
       </c>
       <c r="B30" t="s">
@@ -2928,7 +2941,7 @@
       <c r="F30" t="s">
         <v>116</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" t="s">
         <v>161</v>
       </c>
       <c r="R30" t="s">
@@ -2936,7 +2949,7 @@
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
+      <c r="A31" s="2">
         <v>40848</v>
       </c>
       <c r="B31" t="s">
@@ -2954,7 +2967,7 @@
       <c r="F31" t="s">
         <v>120</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" t="s">
         <v>162</v>
       </c>
       <c r="R31" t="s">
@@ -2962,7 +2975,7 @@
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
+      <c r="A32" s="2">
         <v>40634</v>
       </c>
       <c r="B32" t="s">
@@ -2980,7 +2993,7 @@
       <c r="F32" t="s">
         <v>123</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" t="s">
         <v>163</v>
       </c>
       <c r="R32" t="s">
@@ -2988,7 +3001,7 @@
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
+      <c r="A33" s="2">
         <v>40360</v>
       </c>
       <c r="B33" t="s">
@@ -3006,7 +3019,7 @@
       <c r="F33" t="s">
         <v>126</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" t="s">
         <v>164</v>
       </c>
       <c r="H33" t="s">
@@ -3029,7 +3042,7 @@
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
+      <c r="A34" s="2">
         <v>39264</v>
       </c>
       <c r="B34" t="s">
@@ -3047,7 +3060,7 @@
       <c r="F34" t="s">
         <v>129</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" t="s">
         <v>165</v>
       </c>
       <c r="R34" t="s">
@@ -3055,7 +3068,7 @@
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
+      <c r="A35" s="2">
         <v>44137</v>
       </c>
       <c r="B35" t="s">
@@ -3073,7 +3086,7 @@
       <c r="F35" t="s">
         <v>204</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" t="s">
         <v>201</v>
       </c>
       <c r="H35" t="s">
@@ -3102,7 +3115,7 @@
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
+      <c r="A36" s="2">
         <v>44115</v>
       </c>
       <c r="B36" t="s">
@@ -3120,10 +3133,10 @@
       <c r="F36" t="s">
         <v>215</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" t="s">
         <v>213</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" t="s">
         <v>214</v>
       </c>
       <c r="J36">
@@ -3140,7 +3153,7 @@
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A37" s="3">
+      <c r="A37" s="2">
         <v>44355</v>
       </c>
       <c r="B37" t="s">
@@ -3158,10 +3171,10 @@
       <c r="F37" t="s">
         <v>217</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" t="s">
         <v>216</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" t="s">
         <v>220</v>
       </c>
       <c r="J37">
@@ -3175,7 +3188,7 @@
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
+      <c r="A38" s="2">
         <v>44355</v>
       </c>
       <c r="B38" t="s">
@@ -3193,10 +3206,10 @@
       <c r="F38" t="s">
         <v>224</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" t="s">
         <v>228</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H38" t="s">
         <v>225</v>
       </c>
       <c r="J38">
@@ -3219,16 +3232,16 @@
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
+      <c r="A39" s="2">
         <v>44486</v>
       </c>
       <c r="B39" t="s">
         <v>279</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="3" t="s">
         <v>295</v>
       </c>
       <c r="E39" t="s">
@@ -3237,7 +3250,7 @@
       <c r="F39" t="s">
         <v>232</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" t="s">
         <v>248</v>
       </c>
       <c r="H39" t="s">
@@ -3266,16 +3279,16 @@
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
+      <c r="A40" s="2">
         <v>44486</v>
       </c>
       <c r="B40" t="s">
         <v>240</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="3" t="s">
         <v>295</v>
       </c>
       <c r="E40" t="s">
@@ -3284,7 +3297,7 @@
       <c r="F40" t="s">
         <v>242</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" t="s">
         <v>239</v>
       </c>
       <c r="H40" t="s">
@@ -3313,7 +3326,7 @@
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
+      <c r="A41" s="2">
         <v>44493</v>
       </c>
       <c r="B41" t="s">
@@ -3331,7 +3344,7 @@
       <c r="F41" t="s">
         <v>255</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" t="s">
         <v>256</v>
       </c>
       <c r="L41" t="s">
@@ -3351,7 +3364,7 @@
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
+      <c r="A42" s="2">
         <v>44802</v>
       </c>
       <c r="B42" t="s">
@@ -3369,10 +3382,10 @@
       <c r="F42" t="s">
         <v>264</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" t="s">
         <v>263</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" t="s">
         <v>265</v>
       </c>
       <c r="J42">
@@ -3386,7 +3399,7 @@
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
+      <c r="A43" s="2">
         <v>44652</v>
       </c>
       <c r="B43" t="s">
@@ -3404,7 +3417,7 @@
       <c r="F43" t="s">
         <v>269</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" t="s">
         <v>270</v>
       </c>
       <c r="H43" t="s">
@@ -3418,7 +3431,7 @@
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
+      <c r="A44" s="2">
         <v>44822</v>
       </c>
       <c r="B44" t="s">
@@ -3436,7 +3449,7 @@
       <c r="F44" t="s">
         <v>276</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" t="s">
         <v>272</v>
       </c>
       <c r="R44" t="s">
@@ -3444,7 +3457,7 @@
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
+      <c r="A45" s="2">
         <v>44725</v>
       </c>
       <c r="B45" t="s">
@@ -3462,10 +3475,10 @@
       <c r="F45" t="s">
         <v>280</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" t="s">
         <v>277</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H45" t="s">
         <v>281</v>
       </c>
       <c r="J45">
@@ -3476,7 +3489,7 @@
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
+      <c r="A46" s="2">
         <v>44851</v>
       </c>
       <c r="B46" t="s">
@@ -3494,11 +3507,43 @@
       <c r="F46" t="s">
         <v>286</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" t="s">
         <v>283</v>
       </c>
       <c r="R46" t="s">
         <v>292</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>45190</v>
+      </c>
+      <c r="B47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C47" t="s">
+        <v>320</v>
+      </c>
+      <c r="D47" t="s">
+        <v>294</v>
+      </c>
+      <c r="E47" t="s">
+        <v>347</v>
+      </c>
+      <c r="F47" t="s">
+        <v>344</v>
+      </c>
+      <c r="G47" t="s">
+        <v>345</v>
+      </c>
+      <c r="H47" t="s">
+        <v>346</v>
+      </c>
+      <c r="J47">
+        <v>75</v>
+      </c>
+      <c r="R47" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sripathisridhar/Documents/code/sinc-laboratory.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC652C4E-87EE-F54A-A6CB-481A1EA3DB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0AAE53-DFA3-5E4A-877E-BBFD5CAE991D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="2140" windowWidth="27740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32680" yWindow="-2820" windowWidth="27740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="356">
   <si>
     <t>title</t>
   </si>
@@ -1064,6 +1064,30 @@
   </si>
   <si>
     <t>Sridhar, S., and Cartwright, M. Multi-label Open-set Audio Classification. In &lt;i&gt;Proceedings of the Workshop on Detection and Classification of Acoustic Scenes and Events (DCASE)&lt;/i&gt;, 2023.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.13755902</t>
+  </si>
+  <si>
+    <t>Open-set Tagging (OST) dataset</t>
+  </si>
+  <si>
+    <t>sridhar_icassp25_overview.png</t>
+  </si>
+  <si>
+    <t>sridhar2025compositional_poster.pdf</t>
+  </si>
+  <si>
+    <t>Human auditory perception is compositional in nature — we identify auditory streams from auditory scenes with multiple sound events. However, such auditory scenes are typically represented using clip-level representations that do not disentangle the constituent sound sources. In this work, we learn source-centric audio representations where each sound source is represented using a distinct, disentangled source embedding in the audio representation. We propose two novel approaches to learning source-centric audio representations: a supervised model guided by classification and an unsupervised model guided by feature reconstruction, both of which outperform the baselines. We thoroughly evaluate the design choices of both approaches using an audio classification task. We find that supervision is beneficial to learn source-centric representations, and that reconstructing audio features is more useful than reconstructing spectrograms to learn unsupervised source-centric representations. Leveraging source-centric models can help unlock the potential of greater interpretability and more flexible decoding in machine listening.</t>
+  </si>
+  <si>
+    <t>sridhar2025compositional.pdf</t>
+  </si>
+  <si>
+    <t>Compositional Audio Representation Learning</t>
+  </si>
+  <si>
+    <t>Sridhar, S., &amp; Cartwright, M. (2025, April). Compositional Audio Representation Learning. In ICASSP 2025-2025 IEEE International Conference on Acoustics, Speech and Signal Processing (ICASSP) (pp. 1-5). IEEE.</t>
   </si>
 </sst>
 </file>
@@ -1566,11 +1590,14 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1927,7 +1954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -3543,6 +3570,47 @@
         <v>75</v>
       </c>
       <c r="R47" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>45753</v>
+      </c>
+      <c r="B48" t="s">
+        <v>354</v>
+      </c>
+      <c r="C48" t="s">
+        <v>324</v>
+      </c>
+      <c r="D48" t="s">
+        <v>298</v>
+      </c>
+      <c r="E48" t="s">
+        <v>355</v>
+      </c>
+      <c r="F48" t="s">
+        <v>353</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="H48" t="s">
+        <v>350</v>
+      </c>
+      <c r="J48">
+        <v>75</v>
+      </c>
+      <c r="L48" t="s">
+        <v>351</v>
+      </c>
+      <c r="P48" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>349</v>
+      </c>
+      <c r="R48" t="s">
         <v>289</v>
       </c>
     </row>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sripathisridhar/Documents/code/sinc-laboratory.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0AAE53-DFA3-5E4A-877E-BBFD5CAE991D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A57057-2527-B64A-8885-A7C5186D7556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32680" yWindow="-2820" windowWidth="27740" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -1087,7 +1087,7 @@
     <t>Compositional Audio Representation Learning</t>
   </si>
   <si>
-    <t>Sridhar, S., &amp; Cartwright, M. (2025, April). Compositional Audio Representation Learning. In ICASSP 2025-2025 IEEE International Conference on Acoustics, Speech and Signal Processing (ICASSP) (pp. 1-5). IEEE.</t>
+    <t>Sridhar, S., and Cartwright, M. Compositional Audio Representation Learning. In &lt;i&gt;Proceedings of the IEEE International Conference on Acoustics, Speech and Signal Processing (ICASSP)&lt;/i&gt;, 2025.</t>
   </si>
 </sst>
 </file>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sripathisridhar/Documents/code/sinc-laboratory.github.io/markdown_generator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/keitaohshiro/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A57057-2527-B64A-8885-A7C5186D7556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B95927-D7FB-414D-BF49-D44C64D3CEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="365">
   <si>
     <t>title</t>
   </si>
@@ -1088,6 +1088,33 @@
   </si>
   <si>
     <t>Sridhar, S., and Cartwright, M. Compositional Audio Representation Learning. In &lt;i&gt;Proceedings of the IEEE International Conference on Acoustics, Speech and Signal Processing (ICASSP)&lt;/i&gt;, 2025.</t>
+  </si>
+  <si>
+    <t>Audio engineering by people who are deaf and hard of hearing: balancing confidence and limitations</t>
+  </si>
+  <si>
+    <t>ohshiro2024audioengineering.pdf</t>
+  </si>
+  <si>
+    <t>With technological advancements, audio engineering has evolved from a domain exclusive to professionals to one open to amateurs. However, research is limited on the accessibility of audio engineering, particularly for deaf, Deaf, and hard of hearing (DHH) individuals. To bridge this gap, we interviewed eight deaf and hard of hearing (dHH) audio engineers in music to understand accessibility in audio engineering. We found that their hearing magnified challenges in audio engineering: insecurities in sound perception undermined their confidence, and the required extra “hearing work” added complexity. As workarounds, participants employed various technologies and techniques, relied on the support of hearing peers, and developed strategies for learning and growth. Through these practices, they navigate audio engineering while balancing confidence and limitations. For future directions, we recommend exploring technologies that reduce insecurities and “hearing work” to empower DHH audio engineers and working toward a DHH-community-driven approach to accessible audio engineering.</t>
+  </si>
+  <si>
+    <t>ohshiro2025audioengineering_poster.pdf</t>
+  </si>
+  <si>
+    <t>Audio Engineering for Podcasts by deaf and Hard of Hearing Creators</t>
+  </si>
+  <si>
+    <t>Ohshiro, K., Cartwright, M. Audio Engineering for Podcasts by deaf and Hard of Hearing Creators. In &lt;i&gt;Proceedings of the ACM Conference on Human Factors in Computing Systems (CHI)&lt;/i&gt;, 2025.</t>
+  </si>
+  <si>
+    <t>Ohshiro, K., Cartwright, M. Audio engineering by people who are deaf and hard of hearing: balancing confidence and limitations. In &lt;i&gt;Proceedings of the ACM Conference on Human Factors in Computing Systems (CHI)&lt;/i&gt;, 2024.</t>
+  </si>
+  <si>
+    <t>ohshiro2025audioengineering.pdf</t>
+  </si>
+  <si>
+    <t>Podcasting has evolved as a significant medium where independent creators engage in various production stages, including audio engineering. However, research is limited on how deaf and hard of hearing (dHH) people create podcasts. To address this gap, we conducted interviews with four self-taught dHH podcasters engaged in audio engineering. Our findings reveal how they navigate hearing-related challenges through visual editing techniques, self-taught skill development, and reliance on peer support, while advocating for accessibility. For future directions, we discuss differences between podcast and music audio engineering and recommend integrating AI-powered tools and developing accessible learning resources and environments to support dHH creators.</t>
   </si>
 </sst>
 </file>
@@ -1658,9 +1685,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1698,7 +1725,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1804,7 +1831,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1946,7 +1973,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1954,12 +1981,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R48"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="20" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.83203125" customWidth="1"/>
-    <col min="3" max="4" width="76.6640625" customWidth="1"/>
+    <col min="3" max="3" width="76.6640625" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" customWidth="1"/>
     <col min="6" max="6" width="51.1640625" customWidth="1"/>
     <col min="7" max="7" width="73.33203125" customWidth="1"/>
   </cols>
@@ -3612,6 +3640,61 @@
       </c>
       <c r="R48" t="s">
         <v>289</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>45423</v>
+      </c>
+      <c r="B49" t="s">
+        <v>356</v>
+      </c>
+      <c r="C49" t="s">
+        <v>326</v>
+      </c>
+      <c r="D49" t="s">
+        <v>300</v>
+      </c>
+      <c r="E49" t="s">
+        <v>362</v>
+      </c>
+      <c r="F49" t="s">
+        <v>357</v>
+      </c>
+      <c r="G49" t="s">
+        <v>358</v>
+      </c>
+      <c r="R49" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>45773</v>
+      </c>
+      <c r="B50" t="s">
+        <v>360</v>
+      </c>
+      <c r="C50" t="s">
+        <v>326</v>
+      </c>
+      <c r="D50" t="s">
+        <v>300</v>
+      </c>
+      <c r="E50" t="s">
+        <v>361</v>
+      </c>
+      <c r="F50" t="s">
+        <v>363</v>
+      </c>
+      <c r="G50" t="s">
+        <v>364</v>
+      </c>
+      <c r="L50" t="s">
+        <v>359</v>
+      </c>
+      <c r="R50" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/keitaohshiro/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/markcartwight/git/sinc-laboratory.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B95927-D7FB-414D-BF49-D44C64D3CEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEF214E-7D2C-494C-B7DA-39D7441CBDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3640" yWindow="880" windowWidth="36000" windowHeight="18280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="394">
   <si>
     <t>title</t>
   </si>
@@ -1105,9 +1105,6 @@
     <t>Audio Engineering for Podcasts by deaf and Hard of Hearing Creators</t>
   </si>
   <si>
-    <t>Ohshiro, K., Cartwright, M. Audio Engineering for Podcasts by deaf and Hard of Hearing Creators. In &lt;i&gt;Proceedings of the ACM Conference on Human Factors in Computing Systems (CHI)&lt;/i&gt;, 2025.</t>
-  </si>
-  <si>
     <t>Ohshiro, K., Cartwright, M. Audio engineering by people who are deaf and hard of hearing: balancing confidence and limitations. In &lt;i&gt;Proceedings of the ACM Conference on Human Factors in Computing Systems (CHI)&lt;/i&gt;, 2024.</t>
   </si>
   <si>
@@ -1115,6 +1112,96 @@
   </si>
   <si>
     <t>Podcasting has evolved as a significant medium where independent creators engage in various production stages, including audio engineering. However, research is limited on how deaf and hard of hearing (dHH) people create podcasts. To address this gap, we conducted interviews with four self-taught dHH podcasters engaged in audio engineering. Our findings reveal how they navigate hearing-related challenges through visual editing techniques, self-taught skill development, and reliance on peer support, while advocating for accessibility. For future directions, we discuss differences between podcast and music audio engineering and recommend integrating AI-powered tools and developing accessible learning resources and environments to support dHH creators.</t>
+  </si>
+  <si>
+    <t>cartwright2023does.pdf</t>
+  </si>
+  <si>
+    <t>knight2024individual.pdf</t>
+  </si>
+  <si>
+    <t>anaraky2025role.pdf</t>
+  </si>
+  <si>
+    <t>may2024towards.pdf</t>
+  </si>
+  <si>
+    <t>may2024unspoken.pdf</t>
+  </si>
+  <si>
+    <t>The COVID-19 pandemic had an unprecedented effect in human activity and city landscapes. A very notorious transformation during this period was the change in noise levels and patterns across cities. Small scale studies have show this change in noise levels across different locations in the globe. In this work, we extend these studies by using historical audio data from the SONYC sensor network deployed in New York City. We exploit machine listening models to understand not only noise levels but also patterns, by performing a sound source presence analysis. Finally, we contrast our finding from the acoustic data with noise complaints to better understand the relationship between noise and our perception of it.</t>
+  </si>
+  <si>
+    <t>Does a quiter city mean fewer complaints? The sounds of New York City during the COVID-19 lockdown</t>
+  </si>
+  <si>
+    <t>covid_noise_drop.png</t>
+  </si>
+  <si>
+    <t>cartwright2024does_poster.pdf</t>
+  </si>
+  <si>
+    <t>cartwright2024does_presentation.pdf</t>
+  </si>
+  <si>
+    <t>Cartwright, M., Fuentes, M., Mydlarz, C., Miranda, F., Bello, J.P.  Does a quiter city mean fewer complaints? The sounds of New York City during COVID-19 lockdown. In &lt;i&gt;Proceedings of the IEEE International Conference on Acoustics, Speech and Signal Processing (ICASSP)&lt;/i&gt;, 2023.</t>
+  </si>
+  <si>
+    <t>Recent advances in bioacoustics combined with acoustic individual identification (AIID) could open frontiers for ecological and evolutionary research because traditional methods of identifying individuals are invasive, expensive, labor-intensive, and potentially biased. Despite overwhelming evidence that most taxa have individual acoustic signatures, the application of AIID remains challenging and uncommon. Furthermore, the methods most commonly used for AIID are not compatible with many potential AIID applications. Deep learning in adjacent disciplines suggests opportunities to advance AIID, but such progress is limited by training data. We suggest that broadscale implementation of AIID is achievable, but researchers should prioritize methods that maximize the potential applications of AIID, and develop case studies with easy taxa at smaller spatiotemporal scales before progressing to more difficult scenarios.</t>
+  </si>
+  <si>
+    <t>individual_id_difficulty.png</t>
+  </si>
+  <si>
+    <t>Knight, E.C., Rinehart, T.A., de Zwaan, D, Weldy, M.J., Cartwright, M., Hawley, S., Larkin, J.L., Lesmeister, D., Bayne, E.M., Kitzes, J. Individual Identification in Acoustic Recording. In &lt;i&gt;Trends in Ecology and Evolution&lt;/i&gt;, vol. 39 (9), 2024.</t>
+  </si>
+  <si>
+    <t>TREE</t>
+  </si>
+  <si>
+    <t>Trends in Ecology and Evolution</t>
+  </si>
+  <si>
+    <t>Individual Identification in Acoustic Recording</t>
+  </si>
+  <si>
+    <t>Unspoken Sound: Identifying Trends in Non-Speech Audio Captioning on YouTube</t>
+  </si>
+  <si>
+    <t>May, L., Ohshiro, K., Dang, K., Sridhar, S., Pai, J., Fuentes, M., Lee, S., Cartwright, M. Unspoken Sound: Identifying Trends in Non-Speech Audio Captioning on YouTube. In &lt;i&gt;Proceedings of the ACM Conference on Human Factors in Computing Systems (CHI)&lt;/i&gt;, 2024.</t>
+  </si>
+  <si>
+    <t>High-quality closed captioning of both speech and non-speech elements (e.g., music, sound effects, manner of speaking, and speaker identification) is essential for the accessibility of video content, especially for d/Deaf and hard-of-hearing individuals. While many regions have regulations mandating captioning for television and movies, a regulatory gap remains for the vast amount of web-based video content, including the staggering 500+ hours uploaded to YouTube every minute. Advances in automatic speech recognition have bolstered the presence of captions on YouTube. However, the technology has notable limitations, including the omission of many non-speech elements, which are often crucial for understanding content narratives. This paper examines the contemporary and historical state of non-speech information (NSI) captioning on YouTube through the creation and exploratory analysis of a dataset of over 715k videos. We identify factors that influence NSI caption practices and suggest avenues for future research to enhance the accessibility of online video content.</t>
+  </si>
+  <si>
+    <t>May, L., Williams, A., Hassan, S., Cartwright, M., Lee, S. Towards a Rich Format for Closed Captioning. In &lt;i&gt;Proceedings of the ACM SIGACCESS Conference on Computers and Accessibility (ASSETS)&lt;/i&gt;, 2024.</t>
+  </si>
+  <si>
+    <t>Closed-captioning is an essential part of viewing audio-visual content for many people, including those who are D/deaf and Hard-of-Hearing. Traditional closed-captioning systems generally consist of a single track of timed text that offers limited options for personalization. Research into extending the capabilities of captioning, such as affective, poetic, and customizable captions has shown a desire among a subset of users for these features, but only in specific contexts. However, due to the difficulty in creating custom stimuli videos utilizing the custom captioning system, comparisons between systems and longitudinal studies have not been pursued. This demo paper introduces Rich Captions, a structured system that allows for a single closed-caption file to be tagged with additional information that can then be flexibly leveraged to render different customizable, creative, and poetic captions from the same file. Additionally, we introduce the Rich Caption Editor 1, a free, open-source software system designed to author, edit, and render rich captions. The system design was informed by a formative design workshop with closed-captioning researchers and advocates. The current design allows researchers to generate reproducible stimuli for closed-captioning studies. Once the design space and user preferences are better understood, the rich captioning framework could be refined to serve a general audience.</t>
+  </si>
+  <si>
+    <t>Towards a Rich Format for Closed Captioning</t>
+  </si>
+  <si>
+    <t>rich_caption_example.png</t>
+  </si>
+  <si>
+    <t>access</t>
+  </si>
+  <si>
+    <t>Anaraky, R., Cartwright, M., Nov, O. The Role of Auditory Environments and Anxiety in Detecting Phishing Emails. In &lt;i&gt;Proceedings of the ACM CHI Conference Extended Abstracts on Human Factors in Computing Systems (CHI EA)&lt;/i&gt;, 2025.</t>
+  </si>
+  <si>
+    <t>Ohshiro, K., Cartwright, M. Audio Engineering for Podcasts by deaf and Hard of Hearing Creators. In &lt;i&gt;Proceedings of the ACM Conference Extended Abstracts on Human Factors in Computing Systems (CHI EA)&lt;/i&gt;, 2025.</t>
+  </si>
+  <si>
+    <t>The Role of Auditory Environments and Anxiety in Detecting Phishing Emails</t>
+  </si>
+  <si>
+    <t>This work explores the effects of auditory environments and anxiety on users’ ability to identify phishing emails. In an experimental in-person study, sixty participants evaluated twelve different phishing and legitimate emails while immersed in four different auditory environments (silence, lecture, ambient street noise, concert), at low or high playback (i.e., volume) levels. Using a path model, we found that (1) all non-silent auditory environments induced some level of anxiety, reducing participants’ ability to correctly identify phishing emails, and (2) low (vs. high) playback level of ambient noise led to lower levels of anxiety and, in turn, higher accuracy in identifying phishing emails. These findings highlight the importance of auditory environments in managing anxiety for improving phishing detection capabilities. We discuss the theoretical and practical implications of this work.</t>
+  </si>
+  <si>
+    <t>may2024unspoken_presentation.pdf</t>
   </si>
 </sst>
 </file>
@@ -1685,9 +1772,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1725,7 +1812,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1831,7 +1918,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1973,7 +2060,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1981,13 +2068,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.83203125" customWidth="1"/>
     <col min="3" max="3" width="76.6640625" customWidth="1"/>
     <col min="4" max="4" width="27.33203125" customWidth="1"/>
+    <col min="5" max="5" width="94.6640625" customWidth="1"/>
     <col min="6" max="6" width="51.1640625" customWidth="1"/>
     <col min="7" max="7" width="73.33203125" customWidth="1"/>
   </cols>
@@ -3598,7 +3686,7 @@
         <v>75</v>
       </c>
       <c r="R47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3656,7 +3744,7 @@
         <v>300</v>
       </c>
       <c r="E49" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F49" t="s">
         <v>357</v>
@@ -3679,22 +3767,179 @@
         <v>326</v>
       </c>
       <c r="D50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E50" t="s">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="F50" t="s">
+        <v>362</v>
+      </c>
+      <c r="G50" t="s">
         <v>363</v>
-      </c>
-      <c r="G50" t="s">
-        <v>364</v>
       </c>
       <c r="L50" t="s">
         <v>359</v>
       </c>
       <c r="R50" t="s">
         <v>292</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>45447</v>
+      </c>
+      <c r="B51" t="s">
+        <v>370</v>
+      </c>
+      <c r="C51" t="s">
+        <v>324</v>
+      </c>
+      <c r="D51" t="s">
+        <v>298</v>
+      </c>
+      <c r="E51" t="s">
+        <v>374</v>
+      </c>
+      <c r="F51" t="s">
+        <v>364</v>
+      </c>
+      <c r="G51" t="s">
+        <v>369</v>
+      </c>
+      <c r="H51" t="s">
+        <v>371</v>
+      </c>
+      <c r="J51">
+        <v>75</v>
+      </c>
+      <c r="L51" t="s">
+        <v>372</v>
+      </c>
+      <c r="M51" t="s">
+        <v>373</v>
+      </c>
+      <c r="R51" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>45566</v>
+      </c>
+      <c r="B52" t="s">
+        <v>380</v>
+      </c>
+      <c r="C52" t="s">
+        <v>379</v>
+      </c>
+      <c r="D52" t="s">
+        <v>378</v>
+      </c>
+      <c r="E52" t="s">
+        <v>377</v>
+      </c>
+      <c r="F52" t="s">
+        <v>365</v>
+      </c>
+      <c r="G52" t="s">
+        <v>375</v>
+      </c>
+      <c r="H52" t="s">
+        <v>376</v>
+      </c>
+      <c r="J52">
+        <v>100</v>
+      </c>
+      <c r="R52" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>45773</v>
+      </c>
+      <c r="B53" t="s">
+        <v>391</v>
+      </c>
+      <c r="C53" t="s">
+        <v>326</v>
+      </c>
+      <c r="D53" t="s">
+        <v>299</v>
+      </c>
+      <c r="E53" t="s">
+        <v>389</v>
+      </c>
+      <c r="F53" t="s">
+        <v>366</v>
+      </c>
+      <c r="G53" t="s">
+        <v>392</v>
+      </c>
+      <c r="R53" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>45592</v>
+      </c>
+      <c r="B54" t="s">
+        <v>386</v>
+      </c>
+      <c r="C54" t="s">
+        <v>319</v>
+      </c>
+      <c r="D54" t="s">
+        <v>306</v>
+      </c>
+      <c r="E54" t="s">
+        <v>384</v>
+      </c>
+      <c r="F54" t="s">
+        <v>367</v>
+      </c>
+      <c r="G54" t="s">
+        <v>385</v>
+      </c>
+      <c r="H54" t="s">
+        <v>387</v>
+      </c>
+      <c r="J54">
+        <v>75</v>
+      </c>
+      <c r="R54" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>45423</v>
+      </c>
+      <c r="B55" t="s">
+        <v>381</v>
+      </c>
+      <c r="C55" t="s">
+        <v>326</v>
+      </c>
+      <c r="D55" t="s">
+        <v>300</v>
+      </c>
+      <c r="E55" t="s">
+        <v>382</v>
+      </c>
+      <c r="F55" t="s">
+        <v>368</v>
+      </c>
+      <c r="G55" t="s">
+        <v>383</v>
+      </c>
+      <c r="M55" t="s">
+        <v>393</v>
+      </c>
+      <c r="R55" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/markcartwight/git/sinc-laboratory.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEF214E-7D2C-494C-B7DA-39D7441CBDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08266B5-1714-2B4B-BCF8-6CBD08A9AE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3640" yWindow="880" windowWidth="36000" windowHeight="18280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2220" yWindow="4300" windowWidth="36000" windowHeight="18220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="407">
   <si>
     <t>title</t>
   </si>
@@ -1202,6 +1202,45 @@
   </si>
   <si>
     <t>may2024unspoken_presentation.pdf</t>
+  </si>
+  <si>
+    <t>“Choices? That's the dream”: challenges and opportunities in non-speech information closed-captioning</t>
+  </si>
+  <si>
+    <t>Frontiers</t>
+  </si>
+  <si>
+    <t>May, L., Clemens, M., Dang, K., Ohshiro, K., Sridhar, S., Wee, P., Fuentes, M., Lee, S., Cartwright, M. “Choices? That's the dream”: challenges and opportunities in non-speech information closed-captioning. In &lt;i&gt;Frontiers in Computer Science. Sec.Human-Media Interaction&lt;/i&gt;, vol 7, 2025. 2025</t>
+  </si>
+  <si>
+    <t>may2025choices.pdf</t>
+  </si>
+  <si>
+    <t>Introduction: Access to non-speech information (NSI) in video content is essential to creating accessible and engaging video content, particularly for D/deaf and Hard-of-Hearing (DHH) audiences. In this paper we present an overview of the current state of NSI captioning research, professional practice, and user preferences. Methods: We utilized a comprehensive review approach that combined a systematic literature review methodology with a mixed-methods survey and interview study. 1276 papers were screened with 36 eligible for the final inductive best fit analysis. 168 DHH participants completed an online survey and 15 participated in semi-structured interviews. Additionally, 5 professional captioners participated in semi-structured interviews. Results and discussion: We offer systematic insights into the current challenges related to NSI captioning faced by DHH users and professional captioners, trends in recent NSI captioning research, as well as opportunities for future work that enhance user agency, utilize integrated research methodologies, and broaden community involvement.</t>
+  </si>
+  <si>
+    <t>Expressive Range Characterization of Open Text-to-Audio Models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAAI Conference on Artificial Intelligence and Interactive Digital Entertainment </t>
+  </si>
+  <si>
+    <t>AIIDE</t>
+  </si>
+  <si>
+    <t>Morse, J., Naderi, A., Gaudl, S., Cartwright, M., Hoover, A.K., Nelson, M.J. Expressive Range Characterization of Open Text-to-Audio Models. In &lt;i&gt;Proceedings of the AAAI Conference on Artificial Intelligence and Interactive Digital Entertainment&lt;/i&gt;, 2025.</t>
+  </si>
+  <si>
+    <t>morse2025expressive.pdf</t>
+  </si>
+  <si>
+    <t>Text-to-audio models are a type of generative model that produces audio output in response to a given textual prompt. Although level generators and the properties of the functional content that they create (e.g., playability) dominate most discourse in procedurally generated content (PCG), games that emotionally resonate with players tend to weave together a range of creative and multimodal content (e.g., music, sounds, visuals, narrative tone), and multimodal models have begun seeing at least experimental use for this purpose. However, it remains unclear what exactly such models generate, and with what degree of variability and fidelity: audio is an extremely broad class of output for a generative system to target. Within the PCG community, expressive range analysis (ERA) has been used as a quantitative way to characterize generators' output space, especially for level generators. This paper adapts ERA to text-to-audio models, making the analysis tractable by looking at the expressive range of outputs for specific, fixed prompts. Experiments are conducted by prompting the models with several standardized prompts derived from the Environmental Sound Classification (ESC-50) dataset. The resulting audio is analyzed along key acoustic dimensions (e.g., pitch, loudness, and timbre). More broadly, this paper offers a framework for ERA-based exploratory evaluation of generative audio models.</t>
+  </si>
+  <si>
+    <t>eml,gen</t>
+  </si>
+  <si>
+    <t>Frontiers in Computer Science</t>
   </si>
 </sst>
 </file>
@@ -1704,7 +1743,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1712,6 +1751,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2068,10 +2110,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20" style="2" customWidth="1"/>
+    <col min="1" max="1" width="35.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.83203125" customWidth="1"/>
     <col min="3" max="3" width="76.6640625" customWidth="1"/>
     <col min="4" max="4" width="27.33203125" customWidth="1"/>
@@ -3787,7 +3829,7 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>45447</v>
+        <v>45081</v>
       </c>
       <c r="B51" t="s">
         <v>370</v>
@@ -3940,6 +3982,58 @@
       </c>
       <c r="R55" t="s">
         <v>388</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>45826</v>
+      </c>
+      <c r="B56" t="s">
+        <v>394</v>
+      </c>
+      <c r="C56" t="s">
+        <v>406</v>
+      </c>
+      <c r="D56" t="s">
+        <v>395</v>
+      </c>
+      <c r="E56" t="s">
+        <v>396</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="R56" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B57" t="s">
+        <v>399</v>
+      </c>
+      <c r="C57" t="s">
+        <v>400</v>
+      </c>
+      <c r="D57" t="s">
+        <v>401</v>
+      </c>
+      <c r="E57" t="s">
+        <v>402</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="R57" t="s">
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/markcartwight/git/sinc-laboratory.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08266B5-1714-2B4B-BCF8-6CBD08A9AE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3C36AB-49C6-4846-BE94-E3E95FF69E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2220" yWindow="4300" windowWidth="36000" windowHeight="18220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1640" yWindow="2000" windowWidth="36000" windowHeight="18220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="420">
   <si>
     <t>title</t>
   </si>
@@ -1241,6 +1241,45 @@
   </si>
   <si>
     <t>Frontiers in Computer Science</t>
+  </si>
+  <si>
+    <t>Audiocards: Structured Metadata Improves Audio Language Models for Sound Design</t>
+  </si>
+  <si>
+    <t>sridhar2026audiocards.pdf</t>
+  </si>
+  <si>
+    <t>Sound designers search for sounds in large sound effects libraries using aspects such as sound class or visual context. However, the metadata needed for such search is often missing or incomplete, and requires significant manual effort to add. Existing solutions to automate this task by generating metadata, i.e. captioning, and search using learned embeddings, i.e. text-audio retrieval, are not trained on metadata with the structure and information pertinent to sound design. To this end we propose audiocards, structured metadata grounded in acoustic attributes and sonic descriptors, by exploiting the world knowledge of LLMs. We show that training on audiocards improves downstream text-audio retrieval, descriptive captioning, and metadata generation on professional sound effects libraries. Moreover, audiocards also improve performance on general audio captioning and retrieval over the baseline single-sentence captioning approach. We release a curated dataset of sound effects audiocards to invite further research in audio language modeling for sound design.</t>
+  </si>
+  <si>
+    <t>sridhar2026audiocards_presentation.pdf</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.17237181</t>
+  </si>
+  <si>
+    <t>ASFx Eval Audiocards</t>
+  </si>
+  <si>
+    <t>eml,hcap</t>
+  </si>
+  <si>
+    <t>audiocards_overview.png</t>
+  </si>
+  <si>
+    <t>Sridhar, S., Seetharaman, P., Nieto, O., Cartwright, M., Salamon, J. Audiocards: Structured Metadata Improves Audio Language Models for Sound Design. In &lt;i&gt;Proceedings of the IEEE International Conference on Acoustics, Speech and Signal Processing (ICASSP)&lt;/i&gt;, 2026.</t>
+  </si>
+  <si>
+    <t>Like, Comment &amp; Caption: A Decade of Social Media Video Caption Research (2015–2025)</t>
+  </si>
+  <si>
+    <t>Nguyen, H., McDonnell, E., May, L., Druzenko, A., Saifullah, Z., Cartwright, M., Lee, S. Like, Comment &amp; Caption: A Decade of Social Media Video Caption Research (2015–2025). In &lt;i&gt;Proceedings of the ACM Conference on Human Factors in Computing Systems (CHI)&lt;/i&gt;, 2026.</t>
+  </si>
+  <si>
+    <t>nguygen2026like.pdf</t>
+  </si>
+  <si>
+    <t>As video has become the dominant mode of content on platforms such as YouTube, TikTok, and Instagram, captioning has emerged as a critical factor for accessibility, engagement, and visibility. While prior studies have examined different types of social media video captions or communities’ captioning usage, a systematic synthesis has not been undertaken, leading to the risk of proposing interventions that overlook core platform constraints or miss critical accessibility needs. This paper reviews 36 peer-reviewed papers published between 2015 and 2025 across fields such as Human-Computer Interaction (HCI), accessibility, media studies, education, and language learning. We note that captions operate as collective infrastructure co-produced by viewers, creators, and platforms. Deaf and Hard of Hearing (DHH), neurodivergent, and multilingual viewers depend on captions and increasingly expect mechanisms for feedback, while creators face inadequate tool support. Building on these insights, we propose the framework of Participatory Captioning and suggest design implications, highlighting future directions for social media video caption research.</t>
   </si>
 </sst>
 </file>
@@ -1743,7 +1782,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1751,9 +1790,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2110,7 +2146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.33203125" style="2" customWidth="1"/>
@@ -4000,10 +4036,10 @@
       <c r="E56" t="s">
         <v>396</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" t="s">
         <v>397</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G56" t="s">
         <v>398</v>
       </c>
       <c r="R56" t="s">
@@ -4026,14 +4062,81 @@
       <c r="E57" t="s">
         <v>402</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" t="s">
         <v>403</v>
       </c>
-      <c r="G57" s="7" t="s">
+      <c r="G57" t="s">
         <v>404</v>
       </c>
       <c r="R57" t="s">
         <v>405</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B58" t="s">
+        <v>407</v>
+      </c>
+      <c r="C58" t="s">
+        <v>324</v>
+      </c>
+      <c r="D58" t="s">
+        <v>298</v>
+      </c>
+      <c r="E58" t="s">
+        <v>415</v>
+      </c>
+      <c r="F58" t="s">
+        <v>408</v>
+      </c>
+      <c r="G58" t="s">
+        <v>409</v>
+      </c>
+      <c r="H58" t="s">
+        <v>414</v>
+      </c>
+      <c r="J58">
+        <v>100</v>
+      </c>
+      <c r="M58" t="s">
+        <v>410</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>412</v>
+      </c>
+      <c r="R58" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>46125</v>
+      </c>
+      <c r="B59" t="s">
+        <v>416</v>
+      </c>
+      <c r="C59" t="s">
+        <v>326</v>
+      </c>
+      <c r="D59" t="s">
+        <v>300</v>
+      </c>
+      <c r="E59" t="s">
+        <v>417</v>
+      </c>
+      <c r="F59" t="s">
+        <v>418</v>
+      </c>
+      <c r="G59" t="s">
+        <v>419</v>
+      </c>
+      <c r="R59" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -4046,6 +4149,7 @@
     <hyperlink ref="N20" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="P22" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
     <hyperlink ref="P33" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="P58" r:id="rId9" xr:uid="{F42196A9-24D4-EF40-9E2D-293465B78BD2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/markdown_generator/publications.xlsx
+++ b/markdown_generator/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/markcartwight/git/sinc-laboratory.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3C36AB-49C6-4846-BE94-E3E95FF69E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6566C999-7DD6-E741-B414-F3CF0B9B3498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1640" yWindow="2000" windowWidth="36000" windowHeight="18220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5000" yWindow="1560" windowWidth="36000" windowHeight="18220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -1276,10 +1276,10 @@
     <t>Nguyen, H., McDonnell, E., May, L., Druzenko, A., Saifullah, Z., Cartwright, M., Lee, S. Like, Comment &amp; Caption: A Decade of Social Media Video Caption Research (2015–2025). In &lt;i&gt;Proceedings of the ACM Conference on Human Factors in Computing Systems (CHI)&lt;/i&gt;, 2026.</t>
   </si>
   <si>
-    <t>nguygen2026like.pdf</t>
-  </si>
-  <si>
     <t>As video has become the dominant mode of content on platforms such as YouTube, TikTok, and Instagram, captioning has emerged as a critical factor for accessibility, engagement, and visibility. While prior studies have examined different types of social media video captions or communities’ captioning usage, a systematic synthesis has not been undertaken, leading to the risk of proposing interventions that overlook core platform constraints or miss critical accessibility needs. This paper reviews 36 peer-reviewed papers published between 2015 and 2025 across fields such as Human-Computer Interaction (HCI), accessibility, media studies, education, and language learning. We note that captions operate as collective infrastructure co-produced by viewers, creators, and platforms. Deaf and Hard of Hearing (DHH), neurodivergent, and multilingual viewers depend on captions and increasingly expect mechanisms for feedback, while creators face inadequate tool support. Building on these insights, we propose the framework of Participatory Captioning and suggest design implications, highlighting future directions for social media video caption research.</t>
+  </si>
+  <si>
+    <t>nguyen2026like.pdf</t>
   </si>
 </sst>
 </file>
@@ -4130,10 +4130,10 @@
         <v>417</v>
       </c>
       <c r="F59" t="s">
+        <v>419</v>
+      </c>
+      <c r="G59" t="s">
         <v>418</v>
-      </c>
-      <c r="G59" t="s">
-        <v>419</v>
       </c>
       <c r="R59" t="s">
         <v>388</v>
